--- a/entertainment_forms/046_online_booking_symbols_artists--entertainment_forms.xlsx
+++ b/entertainment_forms/046_online_booking_symbols_artists--entertainment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>category_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Category 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>assigned_to</t>
+          <t>assigned_to_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Assigned To</t>
+          <t>Assigned To 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>category_3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Category 3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>agreement_date</t>
+          <t>agreement_date_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Agreement Date</t>
+          <t>Agreement Date 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>agreement_time</t>
+          <t>agreement_time_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Agreement Time</t>
+          <t>Agreement Time 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>agreement_status</t>
+          <t>agreement_status_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Agreement Status</t>
+          <t>Agreement Status 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>assigned_to</t>
+          <t>assigned_to_3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Assigned To</t>
+          <t>Assigned To 3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>category_4</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Category 4</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1101,9 +1101,9 @@
   <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'international'}</t>
+          <t>international</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'International'}</t>
+          <t>International</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'local'}</t>
+          <t>local</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Local'}</t>
+          <t>Local</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'own'}</t>
+          <t>own</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Own'}</t>
+          <t>Own</t>
         </is>
       </c>
     </row>
@@ -1279,7 +1279,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>category_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1296,7 +1296,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>category_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1347,7 +1347,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>assigned_to_choices</t>
+          <t>assigned_to_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1364,7 +1364,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>assigned_to_choices</t>
+          <t>assigned_to_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1381,7 +1381,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>category_3_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1398,7 +1398,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>category_3_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1415,7 +1415,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>agreement_status_choices</t>
+          <t>agreement_status_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1432,7 +1432,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>agreement_status_choices</t>
+          <t>agreement_status_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1449,7 +1449,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>assigned_to_choices</t>
+          <t>assigned_to_3_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1466,7 +1466,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>assigned_to_choices</t>
+          <t>assigned_to_3_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1483,7 +1483,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>category_4_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1500,7 +1500,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>category_4_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
